--- a/ProjectConfigTable/exgas_config/Datas/#exgas.gameplayTags.xlsx
+++ b/ProjectConfigTable/exgas_config/Datas/#exgas.gameplayTags.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\MyRepo\gameplay-ability-system-for-unity\Public\config\Datas\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\MyRepo\gameplay-ability-system-for-unity\ProjectConfigTable\exgas_config\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C27F055D-24C9-4943-A0A0-7F71FED9D4F7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{47E29A00-3E56-4E4F-BC25-0A2B6EC1655A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="46">
   <si>
     <t>##var</t>
   </si>
@@ -152,6 +152,54 @@
   </si>
   <si>
     <t>事件：正在攻击</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Ability.Defend</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>技能：防御</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Ability.Jump</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>技能：跳跃</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>State</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>State.Buff</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>State.Debuff</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>State.Buff.BulkUp</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>状态</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>状态：正向增益</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>状态：负面增益</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>霸体</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -495,7 +543,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G24"/>
+  <dimension ref="A1:G26"/>
   <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="3" max="3" width="26.5546875" customWidth="1"/>
@@ -635,80 +683,137 @@
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="B11" s="2">
+      <c r="B11">
         <v>2004</v>
       </c>
       <c r="C11" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B12">
+        <v>2005</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B13" s="2">
+        <v>2006</v>
+      </c>
+      <c r="C13" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="D11" s="2" t="s">
+      <c r="D13" s="2" t="s">
         <v>25</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="B12" s="1">
-        <v>300</v>
-      </c>
-      <c r="C12" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="D12" s="2" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="B13" s="1">
-        <v>3001</v>
-      </c>
-      <c r="C13" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="D13" s="2" t="s">
-        <v>29</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B14" s="1">
-        <v>3002</v>
+        <v>300</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B15" s="1">
+        <v>3001</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B16" s="1">
+        <v>3002</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="17" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B17" s="1">
         <v>3003</v>
       </c>
-      <c r="C15" s="2" t="s">
+      <c r="C17" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="D15" s="2" t="s">
+      <c r="D17" s="2" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="B16" s="1"/>
-    </row>
-    <row r="17" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B17" s="1"/>
-    </row>
-    <row r="19" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B19" s="2"/>
-    </row>
-    <row r="20" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B20" s="1"/>
-    </row>
-    <row r="21" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B21" s="1"/>
-    </row>
-    <row r="23" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B23" s="2"/>
-    </row>
-    <row r="24" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B24" s="1"/>
+    <row r="18" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B18" s="1">
+        <v>400</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="19" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B19" s="1">
+        <v>4001</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="20" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B20" s="1">
+        <v>4002</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="21" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B21" s="2">
+        <v>4001001</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="22" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B22" s="1"/>
+    </row>
+    <row r="23" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B23" s="1"/>
+    </row>
+    <row r="25" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B25" s="2"/>
+    </row>
+    <row r="26" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B26" s="1"/>
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>

--- a/ProjectConfigTable/exgas_config/Datas/#exgas.gameplayTags.xlsx
+++ b/ProjectConfigTable/exgas_config/Datas/#exgas.gameplayTags.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\MyRepo\gameplay-ability-system-for-unity\ProjectConfigTable\exgas_config\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{47E29A00-3E56-4E4F-BC25-0A2B6EC1655A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EA97D634-3324-427A-B2C3-5576CA15FEE4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/ProjectConfigTable/exgas_config/Datas/#exgas.gameplayTags.xlsx
+++ b/ProjectConfigTable/exgas_config/Datas/#exgas.gameplayTags.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\MyRepo\gameplay-ability-system-for-unity\ProjectConfigTable\exgas_config\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EA97D634-3324-427A-B2C3-5576CA15FEE4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E22779AD-ED91-4359-8EE8-AAD4F171261A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,12 +20,15 @@
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
+    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="48">
   <si>
     <t>##var</t>
   </si>
@@ -200,6 +203,14 @@
   </si>
   <si>
     <t>霸体</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>State.Buff.SpeedUp</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>状态：移速增加</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -804,7 +815,15 @@
       </c>
     </row>
     <row r="22" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B22" s="1"/>
+      <c r="B22" s="2">
+        <v>4001002</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>47</v>
+      </c>
     </row>
     <row r="23" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B23" s="1"/>

--- a/ProjectConfigTable/exgas_config/Datas/#exgas.gameplayTags.xlsx
+++ b/ProjectConfigTable/exgas_config/Datas/#exgas.gameplayTags.xlsx
@@ -1,21 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27932"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="7" rupBuild="14420"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\MyRepo\gameplay-ability-system-for-unity\ProjectConfigTable\exgas_config\Datas\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\REPO\gameplay-ability-system-for-unity\ProjectConfigTable\exgas_config\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E22779AD-ED91-4359-8EE8-AAD4F171261A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-105" yWindow="-105" windowWidth="23250" windowHeight="12450"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="152511"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -28,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="56">
   <si>
     <t>##var</t>
   </si>
@@ -55,175 +54,228 @@
   </si>
   <si>
     <t>标签描述：标签的定义和作用等</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>标签名: 1.格式（根父级Tag.二次父级Tag.三次父级Tag...）；2. 标签短名要求与c#的变量命名规则一致；3.示例：【Effect】，【Effect.Buff】,【Effect.Debuff】,【Effect.Buff.SpeedUp】</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>Faction</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>Faction.Player</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>Faction.Enemy</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>阵营描述标签</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>玩家阵营</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>敌人阵营</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>Ability</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>技能</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>Ability.Die</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>Ability.Move</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>Ability.Attack</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>技能：死亡</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>技能：移动</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>技能：攻击</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>Ability.Dodge</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>技能：闪避</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>Event</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>事件</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>Event.Moving</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>事件：正在移动</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>Event.Dodging</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>Event.Attacking</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>事件：正在闪避</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>事件：正在攻击</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>Ability.Defend</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>技能：防御</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>Ability.Jump</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>技能：跳跃</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>State</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>State.Buff</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>State.Debuff</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>State.Buff.BulkUp</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>状态</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>状态：正向增益</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>状态：负面增益</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>霸体</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>State.Buff.SpeedUp</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>状态：移速增加</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Guide</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>新手引导</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>Guide</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="2"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.Type1</t>
+    </r>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Guide.Type2</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Guide.Type3</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>新手引导：类型1</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>新手引导：类型2</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>新手引导：类型3</t>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="等线"/>
       <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <family val="2"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -261,22 +313,25 @@
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyFill="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="常规 2" xfId="1" xr:uid="{55324ADC-B395-4A2E-867E-64A197BD9EA7}"/>
+    <cellStyle name="常规 2" xfId="1"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -553,16 +608,16 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:G26"/>
-  <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="3" max="3" width="26.5546875" customWidth="1"/>
-    <col min="4" max="4" width="41.33203125" customWidth="1"/>
-    <col min="6" max="6" width="16.77734375" customWidth="1"/>
+    <col min="3" max="3" width="26.5" customWidth="1"/>
+    <col min="4" max="4" width="41.375" customWidth="1"/>
+    <col min="6" max="6" width="16.75" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -578,7 +633,7 @@
       <c r="E1" s="1"/>
       <c r="F1" s="2"/>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
         <v>4</v>
       </c>
@@ -594,7 +649,7 @@
       <c r="E2" s="1"/>
       <c r="F2" s="2"/>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
         <v>7</v>
       </c>
@@ -610,7 +665,7 @@
       <c r="E3" s="1"/>
       <c r="F3" s="2"/>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A4" s="1"/>
       <c r="B4" s="1">
         <v>100</v>
@@ -625,7 +680,7 @@
       <c r="F4" s="2"/>
       <c r="G4" s="2"/>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A5" s="1"/>
       <c r="B5" s="1">
         <v>1001</v>
@@ -638,7 +693,7 @@
       </c>
       <c r="E5" s="1"/>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
       <c r="B6">
         <v>1002</v>
       </c>
@@ -649,7 +704,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
       <c r="B7" s="2">
         <v>200</v>
       </c>
@@ -660,7 +715,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.2">
       <c r="B8" s="1">
         <v>2001</v>
       </c>
@@ -671,7 +726,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.2">
       <c r="B9" s="1">
         <v>2002</v>
       </c>
@@ -682,7 +737,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.2">
       <c r="B10">
         <v>2003</v>
       </c>
@@ -693,7 +748,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.2">
       <c r="B11">
         <v>2004</v>
       </c>
@@ -704,7 +759,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.2">
       <c r="B12">
         <v>2005</v>
       </c>
@@ -715,7 +770,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.2">
       <c r="B13" s="2">
         <v>2006</v>
       </c>
@@ -726,7 +781,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.2">
       <c r="B14" s="1">
         <v>300</v>
       </c>
@@ -737,7 +792,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.2">
       <c r="B15" s="1">
         <v>3001</v>
       </c>
@@ -748,7 +803,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.2">
       <c r="B16" s="1">
         <v>3002</v>
       </c>
@@ -759,7 +814,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="17" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:4" x14ac:dyDescent="0.2">
       <c r="B17" s="1">
         <v>3003</v>
       </c>
@@ -770,7 +825,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="18" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="18" spans="2:4" x14ac:dyDescent="0.2">
       <c r="B18" s="1">
         <v>400</v>
       </c>
@@ -781,7 +836,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="19" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="19" spans="2:4" x14ac:dyDescent="0.2">
       <c r="B19" s="1">
         <v>4001</v>
       </c>
@@ -792,7 +847,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="20" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="20" spans="2:4" x14ac:dyDescent="0.2">
       <c r="B20" s="1">
         <v>4002</v>
       </c>
@@ -803,7 +858,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="21" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="21" spans="2:4" x14ac:dyDescent="0.2">
       <c r="B21" s="2">
         <v>4001001</v>
       </c>
@@ -814,7 +869,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="22" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="22" spans="2:4" x14ac:dyDescent="0.2">
       <c r="B22" s="2">
         <v>4001002</v>
       </c>
@@ -825,17 +880,52 @@
         <v>47</v>
       </c>
     </row>
-    <row r="23" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B23" s="1"/>
-    </row>
-    <row r="25" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B25" s="2"/>
-    </row>
-    <row r="26" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B26" s="1"/>
+    <row r="23" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B23" s="1">
+        <v>500</v>
+      </c>
+      <c r="C23" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="D23" s="3" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="24" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B24" s="1">
+        <v>5001</v>
+      </c>
+      <c r="C24" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="D24" s="3" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="25" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B25" s="1">
+        <v>5002</v>
+      </c>
+      <c r="C25" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="D25" s="3" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="26" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B26" s="1">
+        <v>5003</v>
+      </c>
+      <c r="C26" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="D26" s="3" t="s">
+        <v>55</v>
+      </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="2" type="noConversion"/>
+  <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/ProjectConfigTable/exgas_config/Datas/#exgas.gameplayTags.xlsx
+++ b/ProjectConfigTable/exgas_config/Datas/#exgas.gameplayTags.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\MyRepo\gameplay-ability-system-for-unity\ProjectConfigTable\exgas_config\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{38DC0288-EE80-46DD-B8CD-0B37A52A5731}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2B509FF3-0CB4-4C9B-8D56-2027A68F2115}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="56">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="58">
   <si>
     <t>##var</t>
   </si>
@@ -193,6 +193,14 @@
   </si>
   <si>
     <t>新手引导：类型3</t>
+  </si>
+  <si>
+    <t>State.Buff.SpCosting</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>状态：耐力消耗中</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -539,8 +547,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D26"/>
+  <dimension ref="A1:D27"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="3" max="3" width="19" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
@@ -795,45 +806,56 @@
     </row>
     <row r="23" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B23">
-        <v>500</v>
+        <v>4001003</v>
       </c>
       <c r="C23" t="s">
-        <v>48</v>
+        <v>56</v>
       </c>
       <c r="D23" t="s">
-        <v>49</v>
+        <v>57</v>
       </c>
     </row>
     <row r="24" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B24">
-        <v>5001</v>
+        <v>500</v>
       </c>
       <c r="C24" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="D24" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
     </row>
     <row r="25" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B25">
-        <v>5002</v>
+        <v>5001</v>
       </c>
       <c r="C25" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="D25" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
     </row>
     <row r="26" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B26">
+        <v>5002</v>
+      </c>
+      <c r="C26" t="s">
+        <v>52</v>
+      </c>
+      <c r="D26" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="27" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B27">
         <v>5003</v>
       </c>
-      <c r="C26" t="s">
+      <c r="C27" t="s">
         <v>54</v>
       </c>
-      <c r="D26" t="s">
+      <c r="D27" t="s">
         <v>55</v>
       </c>
     </row>

--- a/ProjectConfigTable/exgas_config/Datas/#exgas.gameplayTags.xlsx
+++ b/ProjectConfigTable/exgas_config/Datas/#exgas.gameplayTags.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\MyRepo\gameplay-ability-system-for-unity\ProjectConfigTable\exgas_config\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2B509FF3-0CB4-4C9B-8D56-2027A68F2115}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F422C985-AD26-4F4A-9425-40EB9A04CA4F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,12 +33,6 @@
     <t>id</t>
   </si>
   <si>
-    <t>name</t>
-  </si>
-  <si>
-    <t>desc</t>
-  </si>
-  <si>
     <t>##type</t>
   </si>
   <si>
@@ -200,6 +194,14 @@
   </si>
   <si>
     <t>状态：耐力消耗中</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Name</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Desc</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -561,38 +563,38 @@
         <v>1</v>
       </c>
       <c r="C1" t="s">
-        <v>2</v>
+        <v>56</v>
       </c>
       <c r="D1" t="s">
-        <v>3</v>
+        <v>57</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C2" t="s">
         <v>4</v>
       </c>
-      <c r="B2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C2" t="s">
-        <v>6</v>
-      </c>
       <c r="D2" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="B3" t="s">
         <v>1</v>
       </c>
       <c r="C3" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D3" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
@@ -600,10 +602,10 @@
         <v>1000000</v>
       </c>
       <c r="C4" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D4" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
@@ -611,10 +613,10 @@
         <v>1001</v>
       </c>
       <c r="C5" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="D5" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
@@ -622,10 +624,10 @@
         <v>1002</v>
       </c>
       <c r="C6" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="D6" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
@@ -633,10 +635,10 @@
         <v>200</v>
       </c>
       <c r="C7" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="D7" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
@@ -644,10 +646,10 @@
         <v>2001</v>
       </c>
       <c r="C8" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="D8" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
@@ -655,10 +657,10 @@
         <v>2002</v>
       </c>
       <c r="C9" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="D9" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
@@ -666,10 +668,10 @@
         <v>2003</v>
       </c>
       <c r="C10" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D10" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
@@ -677,10 +679,10 @@
         <v>2004</v>
       </c>
       <c r="C11" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="D11" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
@@ -688,10 +690,10 @@
         <v>2005</v>
       </c>
       <c r="C12" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="D12" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
@@ -699,10 +701,10 @@
         <v>2006</v>
       </c>
       <c r="C13" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="D13" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
@@ -710,10 +712,10 @@
         <v>300</v>
       </c>
       <c r="C14" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="D14" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
@@ -721,10 +723,10 @@
         <v>3001</v>
       </c>
       <c r="C15" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="D15" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
@@ -732,10 +734,10 @@
         <v>3002</v>
       </c>
       <c r="C16" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="D16" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
     </row>
     <row r="17" spans="2:4" x14ac:dyDescent="0.25">
@@ -743,10 +745,10 @@
         <v>3003</v>
       </c>
       <c r="C17" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="D17" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
     </row>
     <row r="18" spans="2:4" x14ac:dyDescent="0.25">
@@ -754,10 +756,10 @@
         <v>400</v>
       </c>
       <c r="C18" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="D18" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
     </row>
     <row r="19" spans="2:4" x14ac:dyDescent="0.25">
@@ -765,10 +767,10 @@
         <v>4001</v>
       </c>
       <c r="C19" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="D19" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
     </row>
     <row r="20" spans="2:4" x14ac:dyDescent="0.25">
@@ -776,10 +778,10 @@
         <v>4002</v>
       </c>
       <c r="C20" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="D20" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
     </row>
     <row r="21" spans="2:4" x14ac:dyDescent="0.25">
@@ -787,10 +789,10 @@
         <v>4001001</v>
       </c>
       <c r="C21" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="D21" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
     </row>
     <row r="22" spans="2:4" x14ac:dyDescent="0.25">
@@ -798,10 +800,10 @@
         <v>4001002</v>
       </c>
       <c r="C22" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="D22" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
     </row>
     <row r="23" spans="2:4" x14ac:dyDescent="0.25">
@@ -809,10 +811,10 @@
         <v>4001003</v>
       </c>
       <c r="C23" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="D23" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
     </row>
     <row r="24" spans="2:4" x14ac:dyDescent="0.25">
@@ -820,10 +822,10 @@
         <v>500</v>
       </c>
       <c r="C24" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="D24" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
     </row>
     <row r="25" spans="2:4" x14ac:dyDescent="0.25">
@@ -831,10 +833,10 @@
         <v>5001</v>
       </c>
       <c r="C25" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="D25" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
     </row>
     <row r="26" spans="2:4" x14ac:dyDescent="0.25">
@@ -842,10 +844,10 @@
         <v>5002</v>
       </c>
       <c r="C26" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="D26" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
     </row>
     <row r="27" spans="2:4" x14ac:dyDescent="0.25">
@@ -853,10 +855,10 @@
         <v>5003</v>
       </c>
       <c r="C27" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="D27" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
     </row>
   </sheetData>
